--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25ki/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A67310C-EF2B-3640-84F4-2A3839ECB1B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{038FEE74-3B5F-A545-8098-19AF9B2A27B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -86,9 +86,6 @@
     <t>Vorstellung</t>
   </si>
   <si>
-    <t>synagogue-scroll.jpg</t>
-  </si>
-  <si>
     <t>Leitfrage</t>
   </si>
   <si>
@@ -234,6 +231,9 @@
   </si>
   <si>
     <t>stickies.jpg</t>
+  </si>
+  <si>
+    <t>sound-board.jpg</t>
   </si>
 </sst>
 </file>
@@ -706,7 +706,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -742,7 +742,7 @@
         <v>11</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>12</v>
@@ -751,19 +751,19 @@
         <v>13</v>
       </c>
       <c r="S1" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="T1" s="13" t="s">
+      <c r="U1" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="U1" s="13" t="s">
+      <c r="V1" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="V1" s="13" t="s">
+      <c r="W1" s="13" t="s">
         <v>22</v>
-      </c>
-      <c r="W1" s="13" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -774,43 +774,43 @@
         <v>45975</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2" s="4" t="str">
-        <f>IF(LEN(C2),TEXT(C2, "YYYY-MM-DD") &amp; "-" &amp; B2 &amp; ".md",)</f>
+        <f t="shared" ref="E2:E13" si="0">IF(LEN(C2),TEXT(C2, "YYYY-MM-DD") &amp; "-" &amp; B2 &amp; ".md",)</f>
         <v>2025-11-14-1.md</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>16</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I2" s="7"/>
       <c r="J2" t="str">
-        <f>B2 &amp; ". " &amp; F2 &amp; ": " &amp; H2</f>
+        <f t="shared" ref="J2:J13" si="1">B2 &amp; ". " &amp; F2 &amp; ": " &amp; H2</f>
         <v>1. Einleitung: Vorstellung, Ziele, Was ist KI?</v>
       </c>
       <c r="K2" s="3">
-        <f>B2</f>
+        <f t="shared" ref="K2:K13" si="2">B2</f>
         <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M2" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B2 &amp; ". " &amp; G2,".",""),"&amp;","")," ","-"),"--","-")</f>
+        <f t="shared" ref="M2:M13" si="3">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B2 &amp; ". " &amp; G2,".",""),"&amp;","")," ","-"),"--","-")</f>
         <v>1-Vorstellung</v>
       </c>
       <c r="Q2" t="str">
-        <f>"["&amp;B2&amp;"]"</f>
+        <f t="shared" ref="Q2:Q13" si="4">"["&amp;B2&amp;"]"</f>
         <v>[1]</v>
       </c>
       <c r="R2" s="14" t="str">
-        <f t="shared" ref="R2" si="0">"---
+        <f t="shared" ref="R2" si="5">"---
 layout: post
 " &amp; B$1 &amp; ": " &amp; B2 &amp; "
 " &amp; Q$1 &amp; ": " &amp; Q2 &amp; "
@@ -828,7 +828,7 @@
         <v>2025-11-14-1-slides.md</v>
       </c>
       <c r="T2" s="14" t="str">
-        <f>"---
+        <f t="shared" ref="T2:T13" si="6">"---
 layout: reveal
 title: '"&amp;H2&amp;"'
 author: 'Nathan Gibson'
@@ -929,43 +929,43 @@
         <v>45975</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E3" s="4" t="str">
-        <f>IF(LEN(C3),TEXT(C3, "YYYY-MM-DD") &amp; "-" &amp; B3 &amp; ".md",)</f>
+        <f t="shared" si="0"/>
         <v>2025-11-14-2.md</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J3" t="str">
-        <f>B3 &amp; ". " &amp; F3 &amp; ": " &amp; H3</f>
+        <f t="shared" si="1"/>
         <v>2. Einleitung: KI aus ethischer Sicht</v>
       </c>
       <c r="K3" s="3">
-        <f>B3</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="L3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M3" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B3 &amp; ". " &amp; G3,".",""),"&amp;","")," ","-"),"--","-")</f>
+        <f t="shared" si="3"/>
         <v>2-Ethik</v>
       </c>
       <c r="N3" s="10"/>
       <c r="Q3" t="str">
-        <f>"["&amp;B3&amp;"]"</f>
+        <f t="shared" si="4"/>
         <v>[2]</v>
       </c>
       <c r="R3" s="14" t="str">
-        <f>"---
+        <f t="shared" ref="R3:R13" si="7">"---
 layout: post
 " &amp; B$1 &amp; ": " &amp; B3 &amp; "
 " &amp; Q$1 &amp; ": " &amp; Q3 &amp; "
@@ -979,21 +979,11 @@
 ---</v>
       </c>
       <c r="S3" s="14" t="str">
-        <f t="shared" ref="S3:S13" si="1">_xlfn.REGEXREPLACE(E3,"\.md","-slides.md")</f>
+        <f t="shared" ref="S3:S13" si="8">_xlfn.REGEXREPLACE(E3,"\.md","-slides.md")</f>
         <v>2025-11-14-2-slides.md</v>
       </c>
       <c r="T3" s="14" t="str">
-        <f>"---
-layout: reveal
-title: '"&amp;H3&amp;"'
-author: 'Nathan Gibson'
-session: "&amp;B3&amp;"
-tags: ["&amp;B3&amp;",slides]
-category: slides
-image: "&amp;L3&amp;"
-parallaxBackgroundImage: 'assets/img/"&amp;L3&amp;"'
----
-"</f>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">---
 layout: reveal
 title: 'KI aus ethischer Sicht'
@@ -1007,7 +997,7 @@
 </v>
       </c>
       <c r="U3" s="14" t="str">
-        <f t="shared" ref="U3:U13" si="2">"# Einführung in die 
+        <f t="shared" ref="U3:U13" si="9">"# Einführung in die 
 ### Religionswissenschaft
 {: .r-fit-text}
 ### "&amp;H3&amp;"
@@ -1034,7 +1024,7 @@
 </v>
       </c>
       <c r="V3" s="14" t="str">
-        <f t="shared" ref="V3:V12" si="3">"
+        <f t="shared" ref="V3:V12" si="10">"
 ## Lektüre
 ## Diskussion
 ## Vorschau
@@ -1046,7 +1036,7 @@
 Was gibt es für Daten in der Religionswissenschaft?</v>
       </c>
       <c r="W3" s="14" t="str">
-        <f t="shared" ref="W3:W13" si="4">_xlfn.CONCAT(T3:V3)</f>
+        <f t="shared" ref="W3:W12" si="11">_xlfn.CONCAT(T3:V3)</f>
         <v>---
 layout: reveal
 title: 'KI aus ethischer Sicht'
@@ -1082,48 +1072,43 @@
         <v>45976</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E4" s="4" t="str">
-        <f>IF(LEN(C4),TEXT(C4, "YYYY-MM-DD") &amp; "-" &amp; B4 &amp; ".md",)</f>
+        <f t="shared" si="0"/>
         <v>2025-11-15-3.md</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J4" t="str">
-        <f>B4 &amp; ". " &amp; F4 &amp; ": " &amp; H4</f>
+        <f t="shared" si="1"/>
         <v>3. Einleitung: Was gibt es für Daten in der Religionswissenschaft?</v>
       </c>
       <c r="K4" s="3">
-        <f>B4</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="L4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M4" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4 &amp; ". " &amp; G4,".",""),"&amp;","")," ","-"),"--","-")</f>
+        <f t="shared" si="3"/>
         <v>3-Religionswissenschaftliche-Daten</v>
       </c>
       <c r="N4" s="10"/>
       <c r="Q4" t="str">
-        <f>"["&amp;B4&amp;"]"</f>
+        <f t="shared" si="4"/>
         <v>[3]</v>
       </c>
       <c r="R4" s="14" t="str">
-        <f>"---
-layout: post
-" &amp; B$1 &amp; ": " &amp; B4 &amp; "
-" &amp; Q$1 &amp; ": " &amp; Q4 &amp; "
-level: overview
----"</f>
+        <f t="shared" si="7"/>
         <v>---
 layout: post
 session: 3
@@ -1132,21 +1117,11 @@
 ---</v>
       </c>
       <c r="S4" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>2025-11-15-3-slides.md</v>
       </c>
       <c r="T4" s="14" t="str">
-        <f>"---
-layout: reveal
-title: '"&amp;H4&amp;"'
-author: 'Nathan Gibson'
-session: "&amp;B4&amp;"
-tags: ["&amp;B4&amp;",slides]
-category: slides
-image: "&amp;L4&amp;"
-parallaxBackgroundImage: 'assets/img/"&amp;L4&amp;"'
----
-"</f>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">---
 layout: reveal
 title: 'Was gibt es für Daten in der Religionswissenschaft?'
@@ -1160,7 +1135,7 @@
 </v>
       </c>
       <c r="U4" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve"># Einführung in die 
 ### Religionswissenschaft
 {: .r-fit-text}
@@ -1175,7 +1150,7 @@
 </v>
       </c>
       <c r="V4" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">
 ## Lektüre
 ## Diskussion
@@ -1183,7 +1158,7 @@
 Übungen mit Text- und Spracherkennung</v>
       </c>
       <c r="W4" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v>---
 layout: reveal
 title: 'Was gibt es für Daten in der Religionswissenschaft?'
@@ -1219,48 +1194,43 @@
         <v>45976</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E5" s="4" t="str">
-        <f>IF(LEN(C5),TEXT(C5, "YYYY-MM-DD") &amp; "-" &amp; B5 &amp; ".md",)</f>
+        <f t="shared" si="0"/>
         <v>2025-11-15-4.md</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J5" t="str">
-        <f>B5 &amp; ". " &amp; F5 &amp; ": " &amp; H5</f>
+        <f t="shared" si="1"/>
         <v>4. Machinelles Lernen: Übungen mit Text- und Spracherkennung</v>
       </c>
       <c r="K5" s="3">
-        <f>B5</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="L5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M5" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5 &amp; ". " &amp; G5,".",""),"&amp;","")," ","-"),"--","-")</f>
+        <f t="shared" si="3"/>
         <v>4-Übung-Text-und-Spracherkennung</v>
       </c>
       <c r="N5" s="11"/>
       <c r="Q5" t="str">
-        <f>"["&amp;B5&amp;"]"</f>
+        <f t="shared" si="4"/>
         <v>[4]</v>
       </c>
       <c r="R5" s="14" t="str">
-        <f>"---
-layout: post
-" &amp; B$1 &amp; ": " &amp; B5 &amp; "
-" &amp; Q$1 &amp; ": " &amp; Q5 &amp; "
-level: overview
----"</f>
+        <f t="shared" si="7"/>
         <v>---
 layout: post
 session: 4
@@ -1269,21 +1239,11 @@
 ---</v>
       </c>
       <c r="S5" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>2025-11-15-4-slides.md</v>
       </c>
       <c r="T5" s="14" t="str">
-        <f>"---
-layout: reveal
-title: '"&amp;H5&amp;"'
-author: 'Nathan Gibson'
-session: "&amp;B5&amp;"
-tags: ["&amp;B5&amp;",slides]
-category: slides
-image: "&amp;L5&amp;"
-parallaxBackgroundImage: 'assets/img/"&amp;L5&amp;"'
----
-"</f>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">---
 layout: reveal
 title: 'Übungen mit Text- und Spracherkennung'
@@ -1297,7 +1257,7 @@
 </v>
       </c>
       <c r="U5" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve"># Einführung in die 
 ### Religionswissenschaft
 {: .r-fit-text}
@@ -1312,7 +1272,7 @@
 </v>
       </c>
       <c r="V5" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">
 ## Lektüre
 ## Diskussion
@@ -1320,7 +1280,7 @@
 Was sind LLMs?</v>
       </c>
       <c r="W5" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v>---
 layout: reveal
 title: 'Übungen mit Text- und Spracherkennung'
@@ -1356,48 +1316,43 @@
         <v>45976</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6" s="4" t="str">
-        <f>IF(LEN(C6),TEXT(C6, "YYYY-MM-DD") &amp; "-" &amp; B6 &amp; ".md",)</f>
+        <f t="shared" si="0"/>
         <v>2025-11-15-5.md</v>
       </c>
       <c r="F6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" t="s">
         <v>35</v>
       </c>
-      <c r="H6" t="s">
-        <v>36</v>
-      </c>
       <c r="J6" t="str">
-        <f>B6 &amp; ". " &amp; F6 &amp; ": " &amp; H6</f>
+        <f t="shared" si="1"/>
         <v>5. Machinelles Lernen: Was sind LLMs?</v>
       </c>
       <c r="K6" s="3">
-        <f>B6</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="L6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M6" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6 &amp; ". " &amp; G6,".",""),"&amp;","")," ","-"),"--","-")</f>
+        <f t="shared" si="3"/>
         <v>5-LLMs</v>
       </c>
       <c r="N6" s="15"/>
       <c r="Q6" t="str">
-        <f>"["&amp;B6&amp;"]"</f>
+        <f t="shared" si="4"/>
         <v>[5]</v>
       </c>
       <c r="R6" s="14" t="str">
-        <f>"---
-layout: post
-" &amp; B$1 &amp; ": " &amp; B6 &amp; "
-" &amp; Q$1 &amp; ": " &amp; Q6 &amp; "
-level: overview
----"</f>
+        <f t="shared" si="7"/>
         <v>---
 layout: post
 session: 5
@@ -1406,21 +1361,11 @@
 ---</v>
       </c>
       <c r="S6" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>2025-11-15-5-slides.md</v>
       </c>
       <c r="T6" s="14" t="str">
-        <f>"---
-layout: reveal
-title: '"&amp;H6&amp;"'
-author: 'Nathan Gibson'
-session: "&amp;B6&amp;"
-tags: ["&amp;B6&amp;",slides]
-category: slides
-image: "&amp;L6&amp;"
-parallaxBackgroundImage: 'assets/img/"&amp;L6&amp;"'
----
-"</f>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">---
 layout: reveal
 title: 'Was sind LLMs?'
@@ -1434,7 +1379,7 @@
 </v>
       </c>
       <c r="U6" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve"># Einführung in die 
 ### Religionswissenschaft
 {: .r-fit-text}
@@ -1449,7 +1394,7 @@
 </v>
       </c>
       <c r="V6" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">
 ## Lektüre
 ## Diskussion
@@ -1457,7 +1402,7 @@
 Übungen mit LLMs</v>
       </c>
       <c r="W6" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v>---
 layout: reveal
 title: 'Was sind LLMs?'
@@ -1493,48 +1438,43 @@
         <v>45976</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E7" s="4" t="str">
-        <f>IF(LEN(C7),TEXT(C7, "YYYY-MM-DD") &amp; "-" &amp; B7 &amp; ".md",)</f>
+        <f t="shared" si="0"/>
         <v>2025-11-15-6.md</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J7" t="str">
-        <f>B7 &amp; ". " &amp; F7 &amp; ": " &amp; H7</f>
+        <f t="shared" si="1"/>
         <v>6. Machinelles Lernen: Übungen mit LLMs</v>
       </c>
       <c r="K7" s="3">
-        <f>B7</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="L7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M7" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7 &amp; ". " &amp; G7,".",""),"&amp;","")," ","-"),"--","-")</f>
+        <f t="shared" si="3"/>
         <v>6-Übung-LLMs</v>
       </c>
       <c r="N7" s="9"/>
       <c r="Q7" t="str">
-        <f>"["&amp;B7&amp;"]"</f>
+        <f t="shared" si="4"/>
         <v>[6]</v>
       </c>
       <c r="R7" s="14" t="str">
-        <f>"---
-layout: post
-" &amp; B$1 &amp; ": " &amp; B7 &amp; "
-" &amp; Q$1 &amp; ": " &amp; Q7 &amp; "
-level: overview
----"</f>
+        <f t="shared" si="7"/>
         <v>---
 layout: post
 session: 6
@@ -1543,21 +1483,11 @@
 ---</v>
       </c>
       <c r="S7" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>2025-11-15-6-slides.md</v>
       </c>
       <c r="T7" s="14" t="str">
-        <f>"---
-layout: reveal
-title: '"&amp;H7&amp;"'
-author: 'Nathan Gibson'
-session: "&amp;B7&amp;"
-tags: ["&amp;B7&amp;",slides]
-category: slides
-image: "&amp;L7&amp;"
-parallaxBackgroundImage: 'assets/img/"&amp;L7&amp;"'
----
-"</f>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">---
 layout: reveal
 title: 'Übungen mit LLMs'
@@ -1571,7 +1501,7 @@
 </v>
       </c>
       <c r="U7" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve"># Einführung in die 
 ### Religionswissenschaft
 {: .r-fit-text}
@@ -1586,7 +1516,7 @@
 </v>
       </c>
       <c r="V7" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">
 ## Lektüre
 ## Diskussion
@@ -1594,7 +1524,7 @@
 Wie sollen unterschiedliche Datentypen und -strukturen berücksichtigt werden?</v>
       </c>
       <c r="W7" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v>---
 layout: reveal
 title: 'Übungen mit LLMs'
@@ -1630,48 +1560,43 @@
         <v>45996</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E8" s="4" t="str">
-        <f>IF(LEN(C8),TEXT(C8, "YYYY-MM-DD") &amp; "-" &amp; B8 &amp; ".md",)</f>
+        <f t="shared" si="0"/>
         <v>2025-12-05-7.md</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" t="s">
         <v>40</v>
       </c>
-      <c r="H8" t="s">
-        <v>41</v>
-      </c>
       <c r="J8" t="str">
-        <f>B8 &amp; ". " &amp; F8 &amp; ": " &amp; H8</f>
+        <f t="shared" si="1"/>
         <v>7. Daten: Wie sollen unterschiedliche Datentypen und -strukturen berücksichtigt werden?</v>
       </c>
       <c r="K8" s="3">
-        <f>B8</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="L8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M8" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8 &amp; ". " &amp; G8,".",""),"&amp;","")," ","-"),"--","-")</f>
+        <f t="shared" si="3"/>
         <v>7-Datentypen</v>
       </c>
       <c r="N8" s="12"/>
       <c r="Q8" t="str">
-        <f>"["&amp;B8&amp;"]"</f>
+        <f t="shared" si="4"/>
         <v>[7]</v>
       </c>
       <c r="R8" s="14" t="str">
-        <f>"---
-layout: post
-" &amp; B$1 &amp; ": " &amp; B8 &amp; "
-" &amp; Q$1 &amp; ": " &amp; Q8 &amp; "
-level: overview
----"</f>
+        <f t="shared" si="7"/>
         <v>---
 layout: post
 session: 7
@@ -1680,21 +1605,11 @@
 ---</v>
       </c>
       <c r="S8" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>2025-12-05-7-slides.md</v>
       </c>
       <c r="T8" s="14" t="str">
-        <f>"---
-layout: reveal
-title: '"&amp;H8&amp;"'
-author: 'Nathan Gibson'
-session: "&amp;B8&amp;"
-tags: ["&amp;B8&amp;",slides]
-category: slides
-image: "&amp;L8&amp;"
-parallaxBackgroundImage: 'assets/img/"&amp;L8&amp;"'
----
-"</f>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">---
 layout: reveal
 title: 'Wie sollen unterschiedliche Datentypen und -strukturen berücksichtigt werden?'
@@ -1708,7 +1623,7 @@
 </v>
       </c>
       <c r="U8" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve"># Einführung in die 
 ### Religionswissenschaft
 {: .r-fit-text}
@@ -1723,7 +1638,7 @@
 </v>
       </c>
       <c r="V8" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">
 ## Lektüre
 ## Diskussion
@@ -1731,7 +1646,7 @@
 Wie können gängige Systeme für religionswissenschaftliche Daten fein abgestimmt werden?</v>
       </c>
       <c r="W8" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v>---
 layout: reveal
 title: 'Wie sollen unterschiedliche Datentypen und -strukturen berücksichtigt werden?'
@@ -1767,48 +1682,43 @@
         <v>45996</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E9" s="4" t="str">
-        <f>IF(LEN(C9),TEXT(C9, "YYYY-MM-DD") &amp; "-" &amp; B9 &amp; ".md",)</f>
+        <f t="shared" si="0"/>
         <v>2025-12-05-8.md</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G9" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" t="s">
         <v>42</v>
       </c>
-      <c r="H9" t="s">
-        <v>43</v>
-      </c>
       <c r="J9" t="str">
-        <f>B9 &amp; ". " &amp; F9 &amp; ": " &amp; H9</f>
+        <f t="shared" si="1"/>
         <v>8. Daten: Wie können gängige Systeme für religionswissenschaftliche Daten fein abgestimmt werden?</v>
       </c>
       <c r="K9" s="3">
-        <f>B9</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="L9" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="M9" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9 &amp; ". " &amp; G9,".",""),"&amp;","")," ","-"),"--","-")</f>
+        <f t="shared" si="3"/>
         <v>8-Feinabstimmung</v>
       </c>
       <c r="N9" s="9"/>
       <c r="Q9" t="str">
-        <f>"["&amp;B9&amp;"]"</f>
+        <f t="shared" si="4"/>
         <v>[8]</v>
       </c>
       <c r="R9" s="14" t="str">
-        <f>"---
-layout: post
-" &amp; B$1 &amp; ": " &amp; B9 &amp; "
-" &amp; Q$1 &amp; ": " &amp; Q9 &amp; "
-level: overview
----"</f>
+        <f t="shared" si="7"/>
         <v>---
 layout: post
 session: 8
@@ -1817,21 +1727,11 @@
 ---</v>
       </c>
       <c r="S9" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>2025-12-05-8-slides.md</v>
       </c>
       <c r="T9" s="14" t="str">
-        <f>"---
-layout: reveal
-title: '"&amp;H9&amp;"'
-author: 'Nathan Gibson'
-session: "&amp;B9&amp;"
-tags: ["&amp;B9&amp;",slides]
-category: slides
-image: "&amp;L9&amp;"
-parallaxBackgroundImage: 'assets/img/"&amp;L9&amp;"'
----
-"</f>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">---
 layout: reveal
 title: 'Wie können gängige Systeme für religionswissenschaftliche Daten fein abgestimmt werden?'
@@ -1839,13 +1739,13 @@
 session: 8
 tags: [8,slides]
 category: slides
-image: synagogue-scroll.jpg
-parallaxBackgroundImage: 'assets/img/synagogue-scroll.jpg'
+image: sound-board.jpg
+parallaxBackgroundImage: 'assets/img/sound-board.jpg'
 ---
 </v>
       </c>
       <c r="U9" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve"># Einführung in die 
 ### Religionswissenschaft
 {: .r-fit-text}
@@ -1860,7 +1760,7 @@
 </v>
       </c>
       <c r="V9" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">
 ## Lektüre
 ## Diskussion
@@ -1868,7 +1768,7 @@
 Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden? (Teil I)</v>
       </c>
       <c r="W9" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v>---
 layout: reveal
 title: 'Wie können gängige Systeme für religionswissenschaftliche Daten fein abgestimmt werden?'
@@ -1876,8 +1776,8 @@
 session: 8
 tags: [8,slides]
 category: slides
-image: synagogue-scroll.jpg
-parallaxBackgroundImage: 'assets/img/synagogue-scroll.jpg'
+image: sound-board.jpg
+parallaxBackgroundImage: 'assets/img/sound-board.jpg'
 ---
 # Einführung in die 
 ### Religionswissenschaft
@@ -1904,48 +1804,43 @@
         <v>45997</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E10" s="4" t="str">
-        <f>IF(LEN(C10),TEXT(C10, "YYYY-MM-DD") &amp; "-" &amp; B10 &amp; ".md",)</f>
+        <f t="shared" si="0"/>
         <v>2025-12-06-9.md</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J10" t="str">
-        <f>B10 &amp; ". " &amp; F10 &amp; ": " &amp; H10</f>
+        <f t="shared" si="1"/>
         <v>9. Programmieren: Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden? (Teil I)</v>
       </c>
       <c r="K10" s="3">
-        <f>B10</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="L10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M10" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B10 &amp; ". " &amp; G10,".",""),"&amp;","")," ","-"),"--","-")</f>
+        <f t="shared" si="3"/>
         <v>9-Übung-Datenreinigung-und-analyse-I</v>
       </c>
       <c r="N10" s="9"/>
       <c r="Q10" t="str">
-        <f>"["&amp;B10&amp;"]"</f>
+        <f t="shared" si="4"/>
         <v>[9]</v>
       </c>
       <c r="R10" s="14" t="str">
-        <f>"---
-layout: post
-" &amp; B$1 &amp; ": " &amp; B10 &amp; "
-" &amp; Q$1 &amp; ": " &amp; Q10 &amp; "
-level: overview
----"</f>
+        <f t="shared" si="7"/>
         <v>---
 layout: post
 session: 9
@@ -1954,21 +1849,11 @@
 ---</v>
       </c>
       <c r="S10" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>2025-12-06-9-slides.md</v>
       </c>
       <c r="T10" s="14" t="str">
-        <f>"---
-layout: reveal
-title: '"&amp;H10&amp;"'
-author: 'Nathan Gibson'
-session: "&amp;B10&amp;"
-tags: ["&amp;B10&amp;",slides]
-category: slides
-image: "&amp;L10&amp;"
-parallaxBackgroundImage: 'assets/img/"&amp;L10&amp;"'
----
-"</f>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">---
 layout: reveal
 title: 'Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden? (Teil I)'
@@ -1982,7 +1867,7 @@
 </v>
       </c>
       <c r="U10" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve"># Einführung in die 
 ### Religionswissenschaft
 {: .r-fit-text}
@@ -1997,7 +1882,7 @@
 </v>
       </c>
       <c r="V10" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">
 ## Lektüre
 ## Diskussion
@@ -2005,7 +1890,7 @@
 Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden? (Teil II)</v>
       </c>
       <c r="W10" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v>---
 layout: reveal
 title: 'Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden? (Teil I)'
@@ -2041,48 +1926,43 @@
         <v>45997</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E11" s="4" t="str">
-        <f>IF(LEN(C11),TEXT(C11, "YYYY-MM-DD") &amp; "-" &amp; B11 &amp; ".md",)</f>
+        <f t="shared" si="0"/>
         <v>2025-12-06-10.md</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J11" t="str">
-        <f>B11 &amp; ". " &amp; F11 &amp; ": " &amp; H11</f>
+        <f t="shared" si="1"/>
         <v>10. Programmieren: Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden? (Teil II)</v>
       </c>
       <c r="K11" s="3">
-        <f>B11</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="L11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M11" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B11 &amp; ". " &amp; G11,".",""),"&amp;","")," ","-"),"--","-")</f>
+        <f t="shared" si="3"/>
         <v>10-Übung-Datenreinigung-und-analyse-II</v>
       </c>
       <c r="N11" s="9"/>
       <c r="Q11" t="str">
-        <f>"["&amp;B11&amp;"]"</f>
+        <f t="shared" si="4"/>
         <v>[10]</v>
       </c>
       <c r="R11" s="14" t="str">
-        <f>"---
-layout: post
-" &amp; B$1 &amp; ": " &amp; B11 &amp; "
-" &amp; Q$1 &amp; ": " &amp; Q11 &amp; "
-level: overview
----"</f>
+        <f t="shared" si="7"/>
         <v>---
 layout: post
 session: 10
@@ -2091,21 +1971,11 @@
 ---</v>
       </c>
       <c r="S11" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>2025-12-06-10-slides.md</v>
       </c>
       <c r="T11" s="14" t="str">
-        <f>"---
-layout: reveal
-title: '"&amp;H11&amp;"'
-author: 'Nathan Gibson'
-session: "&amp;B11&amp;"
-tags: ["&amp;B11&amp;",slides]
-category: slides
-image: "&amp;L11&amp;"
-parallaxBackgroundImage: 'assets/img/"&amp;L11&amp;"'
----
-"</f>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">---
 layout: reveal
 title: 'Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden? (Teil II)'
@@ -2119,7 +1989,7 @@
 </v>
       </c>
       <c r="U11" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve"># Einführung in die 
 ### Religionswissenschaft
 {: .r-fit-text}
@@ -2134,7 +2004,7 @@
 </v>
       </c>
       <c r="V11" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">
 ## Lektüre
 ## Diskussion
@@ -2142,7 +2012,7 @@
 Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden? (Teil I)</v>
       </c>
       <c r="W11" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v>---
 layout: reveal
 title: 'Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden? (Teil II)'
@@ -2178,48 +2048,43 @@
         <v>45997</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E12" s="4" t="str">
-        <f>IF(LEN(C12),TEXT(C12, "YYYY-MM-DD") &amp; "-" &amp; B12 &amp; ".md",)</f>
+        <f t="shared" si="0"/>
         <v>2025-12-06-11.md</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J12" t="str">
-        <f>B12 &amp; ". " &amp; F12 &amp; ": " &amp; H12</f>
+        <f t="shared" si="1"/>
         <v>11. Programmieren: Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden? (Teil I)</v>
       </c>
       <c r="K12" s="3">
-        <f>B12</f>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="L12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M12" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B12 &amp; ". " &amp; G12,".",""),"&amp;","")," ","-"),"--","-")</f>
+        <f t="shared" si="3"/>
         <v>11-Übung-Datenvisualisierung-I</v>
       </c>
       <c r="N12" s="9"/>
       <c r="Q12" t="str">
-        <f>"["&amp;B12&amp;"]"</f>
+        <f t="shared" si="4"/>
         <v>[11]</v>
       </c>
       <c r="R12" s="14" t="str">
-        <f>"---
-layout: post
-" &amp; B$1 &amp; ": " &amp; B12 &amp; "
-" &amp; Q$1 &amp; ": " &amp; Q12 &amp; "
-level: overview
----"</f>
+        <f t="shared" si="7"/>
         <v>---
 layout: post
 session: 11
@@ -2228,21 +2093,11 @@
 ---</v>
       </c>
       <c r="S12" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>2025-12-06-11-slides.md</v>
       </c>
       <c r="T12" s="14" t="str">
-        <f>"---
-layout: reveal
-title: '"&amp;H12&amp;"'
-author: 'Nathan Gibson'
-session: "&amp;B12&amp;"
-tags: ["&amp;B12&amp;",slides]
-category: slides
-image: "&amp;L12&amp;"
-parallaxBackgroundImage: 'assets/img/"&amp;L12&amp;"'
----
-"</f>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">---
 layout: reveal
 title: 'Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden? (Teil I)'
@@ -2256,7 +2111,7 @@
 </v>
       </c>
       <c r="U12" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve"># Einführung in die 
 ### Religionswissenschaft
 {: .r-fit-text}
@@ -2271,7 +2126,7 @@
 </v>
       </c>
       <c r="V12" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">
 ## Lektüre
 ## Diskussion
@@ -2279,7 +2134,7 @@
 Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden? (Teil II)</v>
       </c>
       <c r="W12" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v>---
 layout: reveal
 title: 'Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden? (Teil I)'
@@ -2315,48 +2170,43 @@
         <v>45997</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" s="4" t="str">
-        <f>IF(LEN(C13),TEXT(C13, "YYYY-MM-DD") &amp; "-" &amp; B13 &amp; ".md",)</f>
+        <f t="shared" si="0"/>
         <v>2025-12-06-12.md</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J13" t="str">
-        <f>B13 &amp; ". " &amp; F13 &amp; ": " &amp; H13</f>
+        <f t="shared" si="1"/>
         <v>12. Programmieren: Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden? (Teil II)</v>
       </c>
       <c r="K13" s="3">
-        <f>B13</f>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="L13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M13" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13 &amp; ". " &amp; G13,".",""),"&amp;","")," ","-"),"--","-")</f>
+        <f t="shared" si="3"/>
         <v>12-Übung-Datenvisualisierung-II</v>
       </c>
       <c r="N13" s="9"/>
       <c r="Q13" t="str">
-        <f>"["&amp;B13&amp;"]"</f>
+        <f t="shared" si="4"/>
         <v>[12]</v>
       </c>
       <c r="R13" s="14" t="str">
-        <f>"---
-layout: post
-" &amp; B$1 &amp; ": " &amp; B13 &amp; "
-" &amp; Q$1 &amp; ": " &amp; Q13 &amp; "
-level: overview
----"</f>
+        <f t="shared" si="7"/>
         <v>---
 layout: post
 session: 12
@@ -2365,21 +2215,11 @@
 ---</v>
       </c>
       <c r="S13" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>2025-12-06-12-slides.md</v>
       </c>
       <c r="T13" s="14" t="str">
-        <f>"---
-layout: reveal
-title: '"&amp;H13&amp;"'
-author: 'Nathan Gibson'
-session: "&amp;B13&amp;"
-tags: ["&amp;B13&amp;",slides]
-category: slides
-image: "&amp;L13&amp;"
-parallaxBackgroundImage: 'assets/img/"&amp;L13&amp;"'
----
-"</f>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">---
 layout: reveal
 title: 'Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden? (Teil II)'
@@ -2393,7 +2233,7 @@
 </v>
       </c>
       <c r="U13" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve"># Einführung in die 
 ### Religionswissenschaft
 {: .r-fit-text}
@@ -2408,7 +2248,7 @@
 </v>
       </c>
       <c r="V13" s="14" t="str">
-        <f t="shared" ref="V13" si="5">"
+        <f t="shared" ref="V13" si="12">"
 ## Lektüre
 ## Diskussion
 ## Vorschau
@@ -2420,7 +2260,7 @@
 </v>
       </c>
       <c r="W13" s="14" t="str">
-        <f t="shared" ref="W13" si="6">_xlfn.CONCAT(T13:V13)</f>
+        <f t="shared" ref="W13" si="13">_xlfn.CONCAT(T13:V13)</f>
         <v xml:space="preserve">---
 layout: reveal
 title: 'Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden? (Teil II)'

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25ki/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{038FEE74-3B5F-A545-8098-19AF9B2A27B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2161E74-A5C0-2744-8271-8DE313F64D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="79">
   <si>
     <t>blank</t>
   </si>
@@ -134,9 +134,6 @@
     <t>Religionswissenschaftliche Daten</t>
   </si>
   <si>
-    <t>Machinelles Lernen</t>
-  </si>
-  <si>
     <t>LLMs</t>
   </si>
   <si>
@@ -164,30 +161,6 @@
     <t>Wie können gängige Systeme für religionswissenschaftliche Daten fein abgestimmt werden?</t>
   </si>
   <si>
-    <t>Übung Datenreinigung und -analyse I</t>
-  </si>
-  <si>
-    <t>Übung Datenreinigung und -analyse II</t>
-  </si>
-  <si>
-    <t>Übung Datenvisualisierung I</t>
-  </si>
-  <si>
-    <t>Übung Datenvisualisierung II</t>
-  </si>
-  <si>
-    <t>Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden? (Teil I)</t>
-  </si>
-  <si>
-    <t>Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden? (Teil II)</t>
-  </si>
-  <si>
-    <t>Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden? (Teil I)</t>
-  </si>
-  <si>
-    <t>Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden? (Teil II)</t>
-  </si>
-  <si>
     <t>KI aus ethischer Sicht</t>
   </si>
   <si>
@@ -234,6 +207,69 @@
   </si>
   <si>
     <t>sound-board.jpg</t>
+  </si>
+  <si>
+    <t>Maschinelles Lernen</t>
+  </si>
+  <si>
+    <t>Begriffe Datenreinigung und -analyse I</t>
+  </si>
+  <si>
+    <t>Begriffe: Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden?</t>
+  </si>
+  <si>
+    <t>Übungen Datenreinigung und -analyse II</t>
+  </si>
+  <si>
+    <t>Begriffe Datenvisualisierung I</t>
+  </si>
+  <si>
+    <t>Übungen Datenvisualisierung II</t>
+  </si>
+  <si>
+    <t>Übungen: Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden?</t>
+  </si>
+  <si>
+    <t>Begriffe: Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden?</t>
+  </si>
+  <si>
+    <t>Übungen: Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden?</t>
+  </si>
+  <si>
+    <t>Arten von KI unterscheiden.</t>
+  </si>
+  <si>
+    <t>Die ethischen Aspekte eines KI-Einsatzes abwägen. </t>
+  </si>
+  <si>
+    <t>Erfahrungen mit maschinellem Lernen sammeln.</t>
+  </si>
+  <si>
+    <t>Erfahrungen mit LLMs sammeln.</t>
+  </si>
+  <si>
+    <t>Datentypen und Datenstrukturen grundlegend verstehen.</t>
+  </si>
+  <si>
+    <t>Das breite Spektrum religionswissenschaftlicher Daten erfassen.</t>
+  </si>
+  <si>
+    <t>Die Prozesse der Anpassung und der Feinabstimmung von Modellen erfassen.</t>
+  </si>
+  <si>
+    <t>Best Practices des Programmierens mit LLMs bezüglich Datenreinigung und Datenanalyse erfassen.</t>
+  </si>
+  <si>
+    <t>Erfahrungen mit Datenreinigung und Datenanalyse sammeln.</t>
+  </si>
+  <si>
+    <t>Best Practices des Programmierens mit LLMs bezüglich Datenvisualisierung erfassen.</t>
+  </si>
+  <si>
+    <t>Erfahrungen mit Datenvisualisierung sammeln.</t>
+  </si>
+  <si>
+    <t>Die Grundcharakteristika von Large Language Models skizzieren.</t>
   </si>
 </sst>
 </file>
@@ -246,7 +282,7 @@
     <numFmt numFmtId="166" formatCode="dd\.mm"/>
     <numFmt numFmtId="167" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -302,6 +338,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -330,7 +373,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -368,6 +411,7 @@
     <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -684,7 +728,7 @@
     <col min="5" max="5" width="18.6640625" style="6" customWidth="1"/>
     <col min="6" max="6" width="26.83203125" customWidth="1"/>
     <col min="7" max="8" width="42.6640625" customWidth="1"/>
-    <col min="9" max="9" width="61" customWidth="1"/>
+    <col min="9" max="9" width="32.6640625" customWidth="1"/>
     <col min="10" max="10" width="27.1640625" customWidth="1"/>
     <col min="11" max="11" width="13.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.5" bestFit="1" customWidth="1"/>
@@ -799,11 +843,14 @@
         <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="M2" t="str">
         <f t="shared" ref="M2:M13" si="3">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B2 &amp; ". " &amp; G2,".",""),"&amp;","")," ","-"),"--","-")</f>
         <v>1-Vorstellung</v>
+      </c>
+      <c r="O2" s="17" t="s">
+        <v>67</v>
       </c>
       <c r="Q2" t="str">
         <f t="shared" ref="Q2:Q13" si="4">"["&amp;B2&amp;"]"</f>
@@ -865,7 +912,7 @@
 ## Einleitung
 ## Heutiges Lernziel
 "&amp;O2</f>
-        <v xml:space="preserve"># Einführung in die 
+        <v># Einführung in die 
 ### Religionswissenschaft
 {: .r-fit-text}
 ### Vorstellung, Ziele, Was ist KI?
@@ -877,7 +924,7 @@
 ## Projekt
 ## Einleitung
 ## Heutiges Lernziel
-</v>
+Arten von KI unterscheiden.</v>
       </c>
       <c r="V2" s="14" t="str">
         <f>"
@@ -915,6 +962,7 @@
 ## Projekt
 ## Einleitung
 ## Heutiges Lernziel
+Arten von KI unterscheiden.
 ## Lektüre
 ## Diskussion
 ## Vorschau
@@ -942,7 +990,7 @@
         <v>31</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="J3" t="str">
         <f t="shared" si="1"/>
@@ -953,13 +1001,16 @@
         <v>2</v>
       </c>
       <c r="L3" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="M3" t="str">
         <f t="shared" si="3"/>
         <v>2-Ethik</v>
       </c>
       <c r="N3" s="10"/>
+      <c r="O3" s="17" t="s">
+        <v>68</v>
+      </c>
       <c r="Q3" t="str">
         <f t="shared" si="4"/>
         <v>[2]</v>
@@ -1010,18 +1061,19 @@
 ## Einleitung
 ## Heutiges Lernziel
 "&amp;O3</f>
-        <v xml:space="preserve"># Einführung in die 
+        <v># Einführung in die 
 ### Religionswissenschaft
 {: .r-fit-text}
 ### KI aus ethischer Sicht
 Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-## 📈 Rückblick: 
-## Projekt
-## Einleitung
-## Heutiges Lernziel
-</v>
+Arten von KI unterscheiden.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Die ethischen Aspekte eines KI-Einsatzes abwägen. </v>
       </c>
       <c r="V3" s="14" t="str">
         <f t="shared" ref="V3:V12" si="10">"
@@ -1054,10 +1106,12 @@
 Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-## 📈 Rückblick: 
-## Projekt
-## Einleitung
-## Heutiges Lernziel
+Arten von KI unterscheiden.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Die ethischen Aspekte eines KI-Einsatzes abwägen. 
 ## Lektüre
 ## Diskussion
 ## Vorschau
@@ -1096,13 +1150,16 @@
         <v>3</v>
       </c>
       <c r="L4" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="M4" t="str">
         <f t="shared" si="3"/>
         <v>3-Religionswissenschaftliche-Daten</v>
       </c>
       <c r="N4" s="10"/>
+      <c r="O4" s="17" t="s">
+        <v>72</v>
+      </c>
       <c r="Q4" t="str">
         <f t="shared" si="4"/>
         <v>[3]</v>
@@ -1136,18 +1193,19 @@
       </c>
       <c r="U4" s="14" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"># Einführung in die 
+        <v># Einführung in die 
 ### Religionswissenschaft
 {: .r-fit-text}
 ### Was gibt es für Daten in der Religionswissenschaft?
 Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-## 📈 Rückblick: 
-## Projekt
-## Einleitung
-## Heutiges Lernziel
-</v>
+Die ethischen Aspekte eines KI-Einsatzes abwägen. 
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Das breite Spektrum religionswissenschaftlicher Daten erfassen.</v>
       </c>
       <c r="V4" s="14" t="str">
         <f t="shared" si="10"/>
@@ -1176,10 +1234,12 @@
 Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-## 📈 Rückblick: 
-## Projekt
-## Einleitung
-## Heutiges Lernziel
+Die ethischen Aspekte eines KI-Einsatzes abwägen. 
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Das breite Spektrum religionswissenschaftlicher Daten erfassen.
 ## Lektüre
 ## Diskussion
 ## Vorschau
@@ -1201,30 +1261,33 @@
         <v>2025-11-15-4.md</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="J5" t="str">
         <f t="shared" si="1"/>
-        <v>4. Machinelles Lernen: Übungen mit Text- und Spracherkennung</v>
+        <v>4. Maschinelles Lernen: Übungen mit Text- und Spracherkennung</v>
       </c>
       <c r="K5" s="3">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="L5" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="M5" t="str">
         <f t="shared" si="3"/>
         <v>4-Übung-Text-und-Spracherkennung</v>
       </c>
       <c r="N5" s="11"/>
+      <c r="O5" s="17" t="s">
+        <v>69</v>
+      </c>
       <c r="Q5" t="str">
         <f t="shared" si="4"/>
         <v>[4]</v>
@@ -1258,18 +1321,19 @@
       </c>
       <c r="U5" s="14" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"># Einführung in die 
+        <v># Einführung in die 
 ### Religionswissenschaft
 {: .r-fit-text}
 ### Übungen mit Text- und Spracherkennung
 Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-## 📈 Rückblick: 
-## Projekt
-## Einleitung
-## Heutiges Lernziel
-</v>
+Das breite Spektrum religionswissenschaftlicher Daten erfassen.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Erfahrungen mit maschinellem Lernen sammeln.</v>
       </c>
       <c r="V5" s="14" t="str">
         <f t="shared" si="10"/>
@@ -1298,10 +1362,12 @@
 Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-## 📈 Rückblick: 
-## Projekt
-## Einleitung
-## Heutiges Lernziel
+Das breite Spektrum religionswissenschaftlicher Daten erfassen.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Erfahrungen mit maschinellem Lernen sammeln.
 ## Lektüre
 ## Diskussion
 ## Vorschau
@@ -1323,30 +1389,33 @@
         <v>2025-11-15-5.md</v>
       </c>
       <c r="F6" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" t="s">
         <v>34</v>
-      </c>
-      <c r="H6" t="s">
-        <v>35</v>
       </c>
       <c r="J6" t="str">
         <f t="shared" si="1"/>
-        <v>5. Machinelles Lernen: Was sind LLMs?</v>
+        <v>5. Maschinelles Lernen: Was sind LLMs?</v>
       </c>
       <c r="K6" s="3">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="L6" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="M6" t="str">
         <f t="shared" si="3"/>
         <v>5-LLMs</v>
       </c>
       <c r="N6" s="15"/>
+      <c r="O6" s="17" t="s">
+        <v>78</v>
+      </c>
       <c r="Q6" t="str">
         <f t="shared" si="4"/>
         <v>[5]</v>
@@ -1380,18 +1449,19 @@
       </c>
       <c r="U6" s="14" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"># Einführung in die 
+        <v># Einführung in die 
 ### Religionswissenschaft
 {: .r-fit-text}
 ### Was sind LLMs?
 Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-## 📈 Rückblick: 
-## Projekt
-## Einleitung
-## Heutiges Lernziel
-</v>
+Erfahrungen mit maschinellem Lernen sammeln.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Die Grundcharakteristika von Large Language Models skizzieren.</v>
       </c>
       <c r="V6" s="14" t="str">
         <f t="shared" si="10"/>
@@ -1420,10 +1490,12 @@
 Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-## 📈 Rückblick: 
-## Projekt
-## Einleitung
-## Heutiges Lernziel
+Erfahrungen mit maschinellem Lernen sammeln.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Die Grundcharakteristika von Large Language Models skizzieren.
 ## Lektüre
 ## Diskussion
 ## Vorschau
@@ -1445,30 +1517,33 @@
         <v>2025-11-15-6.md</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="1"/>
-        <v>6. Machinelles Lernen: Übungen mit LLMs</v>
+        <v>6. Maschinelles Lernen: Übungen mit LLMs</v>
       </c>
       <c r="K7" s="3">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="L7" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="M7" t="str">
         <f t="shared" si="3"/>
         <v>6-Übung-LLMs</v>
       </c>
       <c r="N7" s="9"/>
+      <c r="O7" s="17" t="s">
+        <v>70</v>
+      </c>
       <c r="Q7" t="str">
         <f t="shared" si="4"/>
         <v>[6]</v>
@@ -1502,18 +1577,19 @@
       </c>
       <c r="U7" s="14" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"># Einführung in die 
+        <v># Einführung in die 
 ### Religionswissenschaft
 {: .r-fit-text}
 ### Übungen mit LLMs
 Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-## 📈 Rückblick: 
-## Projekt
-## Einleitung
-## Heutiges Lernziel
-</v>
+Die Grundcharakteristika von Large Language Models skizzieren.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Erfahrungen mit LLMs sammeln.</v>
       </c>
       <c r="V7" s="14" t="str">
         <f t="shared" si="10"/>
@@ -1542,10 +1618,12 @@
 Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-## 📈 Rückblick: 
-## Projekt
-## Einleitung
-## Heutiges Lernziel
+Die Grundcharakteristika von Large Language Models skizzieren.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Erfahrungen mit LLMs sammeln.
 ## Lektüre
 ## Diskussion
 ## Vorschau
@@ -1567,13 +1645,13 @@
         <v>2025-12-05-7.md</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" t="s">
         <v>39</v>
-      </c>
-      <c r="H8" t="s">
-        <v>40</v>
       </c>
       <c r="J8" t="str">
         <f t="shared" si="1"/>
@@ -1584,13 +1662,16 @@
         <v>7</v>
       </c>
       <c r="L8" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="M8" t="str">
         <f t="shared" si="3"/>
         <v>7-Datentypen</v>
       </c>
       <c r="N8" s="12"/>
+      <c r="O8" s="17" t="s">
+        <v>71</v>
+      </c>
       <c r="Q8" t="str">
         <f t="shared" si="4"/>
         <v>[7]</v>
@@ -1624,18 +1705,19 @@
       </c>
       <c r="U8" s="14" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"># Einführung in die 
+        <v># Einführung in die 
 ### Religionswissenschaft
 {: .r-fit-text}
 ### Wie sollen unterschiedliche Datentypen und -strukturen berücksichtigt werden?
 Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-## 📈 Rückblick: 
-## Projekt
-## Einleitung
-## Heutiges Lernziel
-</v>
+Erfahrungen mit LLMs sammeln.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Datentypen und Datenstrukturen grundlegend verstehen.</v>
       </c>
       <c r="V8" s="14" t="str">
         <f t="shared" si="10"/>
@@ -1664,10 +1746,12 @@
 Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-## 📈 Rückblick: 
-## Projekt
-## Einleitung
-## Heutiges Lernziel
+Erfahrungen mit LLMs sammeln.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Datentypen und Datenstrukturen grundlegend verstehen.
 ## Lektüre
 ## Diskussion
 ## Vorschau
@@ -1689,13 +1773,13 @@
         <v>2025-12-05-8.md</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" t="s">
         <v>41</v>
-      </c>
-      <c r="H9" t="s">
-        <v>42</v>
       </c>
       <c r="J9" t="str">
         <f t="shared" si="1"/>
@@ -1706,13 +1790,16 @@
         <v>8</v>
       </c>
       <c r="L9" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="M9" t="str">
         <f t="shared" si="3"/>
         <v>8-Feinabstimmung</v>
       </c>
       <c r="N9" s="9"/>
+      <c r="O9" s="17" t="s">
+        <v>73</v>
+      </c>
       <c r="Q9" t="str">
         <f t="shared" si="4"/>
         <v>[8]</v>
@@ -1746,18 +1833,19 @@
       </c>
       <c r="U9" s="14" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"># Einführung in die 
+        <v># Einführung in die 
 ### Religionswissenschaft
 {: .r-fit-text}
 ### Wie können gängige Systeme für religionswissenschaftliche Daten fein abgestimmt werden?
 Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-## 📈 Rückblick: 
-## Projekt
-## Einleitung
-## Heutiges Lernziel
-</v>
+Datentypen und Datenstrukturen grundlegend verstehen.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Die Prozesse der Anpassung und der Feinabstimmung von Modellen erfassen.</v>
       </c>
       <c r="V9" s="14" t="str">
         <f t="shared" si="10"/>
@@ -1765,7 +1853,7 @@
 ## Lektüre
 ## Diskussion
 ## Vorschau
-Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden? (Teil I)</v>
+Begriffe: Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden?</v>
       </c>
       <c r="W9" s="14" t="str">
         <f t="shared" si="11"/>
@@ -1786,14 +1874,16 @@
 Wintersemester 2025/2026
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
-## 📈 Rückblick: 
-## Projekt
-## Einleitung
-## Heutiges Lernziel
-## Lektüre
-## Diskussion
-## Vorschau
-Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden? (Teil I)</v>
+Datentypen und Datenstrukturen grundlegend verstehen.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Die Prozesse der Anpassung und der Feinabstimmung von Modellen erfassen.
+## Lektüre
+## Diskussion
+## Vorschau
+Begriffe: Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden?</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -1811,30 +1901,33 @@
         <v>2025-12-06-9.md</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="H10" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="J10" t="str">
         <f t="shared" si="1"/>
-        <v>9. Programmieren: Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden? (Teil I)</v>
+        <v>9. Programmieren: Begriffe: Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden?</v>
       </c>
       <c r="K10" s="3">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="L10" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="M10" t="str">
         <f t="shared" si="3"/>
-        <v>9-Übung-Datenreinigung-und-analyse-I</v>
+        <v>9-Begriffe-Datenreinigung-und-analyse-I</v>
       </c>
       <c r="N10" s="9"/>
+      <c r="O10" s="17" t="s">
+        <v>74</v>
+      </c>
       <c r="Q10" t="str">
         <f t="shared" si="4"/>
         <v>[9]</v>
@@ -1856,7 +1949,7 @@
         <f t="shared" si="6"/>
         <v xml:space="preserve">---
 layout: reveal
-title: 'Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden? (Teil I)'
+title: 'Begriffe: Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden?'
 author: 'Nathan Gibson'
 session: 9
 tags: [9,slides]
@@ -1868,18 +1961,19 @@
       </c>
       <c r="U10" s="14" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"># Einführung in die 
-### Religionswissenschaft
-{: .r-fit-text}
-### Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden? (Teil I)
-Wintersemester 2025/2026
-Prof. Dr. Nathan Gibson
-## 📈 Rückblick: Lernziel
-## 📈 Rückblick: 
-## Projekt
-## Einleitung
-## Heutiges Lernziel
-</v>
+        <v># Einführung in die 
+### Religionswissenschaft
+{: .r-fit-text}
+### Begriffe: Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden?
+Wintersemester 2025/2026
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Die Prozesse der Anpassung und der Feinabstimmung von Modellen erfassen.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Best Practices des Programmierens mit LLMs bezüglich Datenreinigung und Datenanalyse erfassen.</v>
       </c>
       <c r="V10" s="14" t="str">
         <f t="shared" si="10"/>
@@ -1887,13 +1981,13 @@
 ## Lektüre
 ## Diskussion
 ## Vorschau
-Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden? (Teil II)</v>
+Übungen: Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden?</v>
       </c>
       <c r="W10" s="14" t="str">
         <f t="shared" si="11"/>
         <v>---
 layout: reveal
-title: 'Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden? (Teil I)'
+title: 'Begriffe: Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden?'
 author: 'Nathan Gibson'
 session: 9
 tags: [9,slides]
@@ -1904,18 +1998,20 @@
 # Einführung in die 
 ### Religionswissenschaft
 {: .r-fit-text}
-### Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden? (Teil I)
-Wintersemester 2025/2026
-Prof. Dr. Nathan Gibson
-## 📈 Rückblick: Lernziel
-## 📈 Rückblick: 
-## Projekt
-## Einleitung
-## Heutiges Lernziel
-## Lektüre
-## Diskussion
-## Vorschau
-Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden? (Teil II)</v>
+### Begriffe: Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden?
+Wintersemester 2025/2026
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Die Prozesse der Anpassung und der Feinabstimmung von Modellen erfassen.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Best Practices des Programmierens mit LLMs bezüglich Datenreinigung und Datenanalyse erfassen.
+## Lektüre
+## Diskussion
+## Vorschau
+Übungen: Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden?</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -1933,30 +2029,33 @@
         <v>2025-12-06-10.md</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="H11" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="J11" t="str">
         <f t="shared" si="1"/>
-        <v>10. Programmieren: Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden? (Teil II)</v>
+        <v>10. Programmieren: Übungen: Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden?</v>
       </c>
       <c r="K11" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="L11" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="M11" t="str">
         <f t="shared" si="3"/>
-        <v>10-Übung-Datenreinigung-und-analyse-II</v>
+        <v>10-Übungen-Datenreinigung-und-analyse-II</v>
       </c>
       <c r="N11" s="9"/>
+      <c r="O11" s="17" t="s">
+        <v>75</v>
+      </c>
       <c r="Q11" t="str">
         <f t="shared" si="4"/>
         <v>[10]</v>
@@ -1978,7 +2077,7 @@
         <f t="shared" si="6"/>
         <v xml:space="preserve">---
 layout: reveal
-title: 'Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden? (Teil II)'
+title: 'Übungen: Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden?'
 author: 'Nathan Gibson'
 session: 10
 tags: [10,slides]
@@ -1990,18 +2089,19 @@
       </c>
       <c r="U11" s="14" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"># Einführung in die 
-### Religionswissenschaft
-{: .r-fit-text}
-### Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden? (Teil II)
-Wintersemester 2025/2026
-Prof. Dr. Nathan Gibson
-## 📈 Rückblick: Lernziel
-## 📈 Rückblick: 
-## Projekt
-## Einleitung
-## Heutiges Lernziel
-</v>
+        <v># Einführung in die 
+### Religionswissenschaft
+{: .r-fit-text}
+### Übungen: Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden?
+Wintersemester 2025/2026
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Best Practices des Programmierens mit LLMs bezüglich Datenreinigung und Datenanalyse erfassen.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Erfahrungen mit Datenreinigung und Datenanalyse sammeln.</v>
       </c>
       <c r="V11" s="14" t="str">
         <f t="shared" si="10"/>
@@ -2009,13 +2109,13 @@
 ## Lektüre
 ## Diskussion
 ## Vorschau
-Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden? (Teil I)</v>
+Begriffe: Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden?</v>
       </c>
       <c r="W11" s="14" t="str">
         <f t="shared" si="11"/>
         <v>---
 layout: reveal
-title: 'Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden? (Teil II)'
+title: 'Übungen: Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden?'
 author: 'Nathan Gibson'
 session: 10
 tags: [10,slides]
@@ -2026,18 +2126,20 @@
 # Einführung in die 
 ### Religionswissenschaft
 {: .r-fit-text}
-### Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden? (Teil II)
-Wintersemester 2025/2026
-Prof. Dr. Nathan Gibson
-## 📈 Rückblick: Lernziel
-## 📈 Rückblick: 
-## Projekt
-## Einleitung
-## Heutiges Lernziel
-## Lektüre
-## Diskussion
-## Vorschau
-Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden? (Teil I)</v>
+### Übungen: Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden?
+Wintersemester 2025/2026
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Best Practices des Programmierens mit LLMs bezüglich Datenreinigung und Datenanalyse erfassen.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Erfahrungen mit Datenreinigung und Datenanalyse sammeln.
+## Lektüre
+## Diskussion
+## Vorschau
+Begriffe: Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden?</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -2055,30 +2157,33 @@
         <v>2025-12-06-11.md</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="H12" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="J12" t="str">
         <f t="shared" si="1"/>
-        <v>11. Programmieren: Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden? (Teil I)</v>
+        <v>11. Programmieren: Begriffe: Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden?</v>
       </c>
       <c r="K12" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="L12" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="M12" t="str">
         <f t="shared" si="3"/>
-        <v>11-Übung-Datenvisualisierung-I</v>
+        <v>11-Begriffe-Datenvisualisierung-I</v>
       </c>
       <c r="N12" s="9"/>
+      <c r="O12" s="17" t="s">
+        <v>76</v>
+      </c>
       <c r="Q12" t="str">
         <f t="shared" si="4"/>
         <v>[11]</v>
@@ -2100,7 +2205,7 @@
         <f t="shared" si="6"/>
         <v xml:space="preserve">---
 layout: reveal
-title: 'Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden? (Teil I)'
+title: 'Begriffe: Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden?'
 author: 'Nathan Gibson'
 session: 11
 tags: [11,slides]
@@ -2112,18 +2217,19 @@
       </c>
       <c r="U12" s="14" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"># Einführung in die 
-### Religionswissenschaft
-{: .r-fit-text}
-### Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden? (Teil I)
-Wintersemester 2025/2026
-Prof. Dr. Nathan Gibson
-## 📈 Rückblick: Lernziel
-## 📈 Rückblick: 
-## Projekt
-## Einleitung
-## Heutiges Lernziel
-</v>
+        <v># Einführung in die 
+### Religionswissenschaft
+{: .r-fit-text}
+### Begriffe: Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden?
+Wintersemester 2025/2026
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Erfahrungen mit Datenreinigung und Datenanalyse sammeln.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Best Practices des Programmierens mit LLMs bezüglich Datenvisualisierung erfassen.</v>
       </c>
       <c r="V12" s="14" t="str">
         <f t="shared" si="10"/>
@@ -2131,13 +2237,13 @@
 ## Lektüre
 ## Diskussion
 ## Vorschau
-Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden? (Teil II)</v>
+Übungen: Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden?</v>
       </c>
       <c r="W12" s="14" t="str">
         <f t="shared" si="11"/>
         <v>---
 layout: reveal
-title: 'Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden? (Teil I)'
+title: 'Begriffe: Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden?'
 author: 'Nathan Gibson'
 session: 11
 tags: [11,slides]
@@ -2148,18 +2254,20 @@
 # Einführung in die 
 ### Religionswissenschaft
 {: .r-fit-text}
-### Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden? (Teil I)
-Wintersemester 2025/2026
-Prof. Dr. Nathan Gibson
-## 📈 Rückblick: Lernziel
-## 📈 Rückblick: 
-## Projekt
-## Einleitung
-## Heutiges Lernziel
-## Lektüre
-## Diskussion
-## Vorschau
-Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden? (Teil II)</v>
+### Begriffe: Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden?
+Wintersemester 2025/2026
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Erfahrungen mit Datenreinigung und Datenanalyse sammeln.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Best Practices des Programmierens mit LLMs bezüglich Datenvisualisierung erfassen.
+## Lektüre
+## Diskussion
+## Vorschau
+Übungen: Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden?</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -2177,30 +2285,33 @@
         <v>2025-12-06-12.md</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="H13" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
-        <v>12. Programmieren: Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden? (Teil II)</v>
+        <v>12. Programmieren: Übungen: Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden?</v>
       </c>
       <c r="K13" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="L13" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="M13" t="str">
         <f t="shared" si="3"/>
-        <v>12-Übung-Datenvisualisierung-II</v>
+        <v>12-Übungen-Datenvisualisierung-II</v>
       </c>
       <c r="N13" s="9"/>
+      <c r="O13" s="17" t="s">
+        <v>77</v>
+      </c>
       <c r="Q13" t="str">
         <f t="shared" si="4"/>
         <v>[12]</v>
@@ -2222,7 +2333,7 @@
         <f t="shared" si="6"/>
         <v xml:space="preserve">---
 layout: reveal
-title: 'Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden? (Teil II)'
+title: 'Übungen: Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden?'
 author: 'Nathan Gibson'
 session: 12
 tags: [12,slides]
@@ -2234,18 +2345,19 @@
       </c>
       <c r="U13" s="14" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"># Einführung in die 
-### Religionswissenschaft
-{: .r-fit-text}
-### Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden? (Teil II)
-Wintersemester 2025/2026
-Prof. Dr. Nathan Gibson
-## 📈 Rückblick: Lernziel
-## 📈 Rückblick: 
-## Projekt
-## Einleitung
-## Heutiges Lernziel
-</v>
+        <v># Einführung in die 
+### Religionswissenschaft
+{: .r-fit-text}
+### Übungen: Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden?
+Wintersemester 2025/2026
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Best Practices des Programmierens mit LLMs bezüglich Datenvisualisierung erfassen.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Erfahrungen mit Datenvisualisierung sammeln.</v>
       </c>
       <c r="V13" s="14" t="str">
         <f t="shared" ref="V13" si="12">"
@@ -2263,7 +2375,7 @@
         <f t="shared" ref="W13" si="13">_xlfn.CONCAT(T13:V13)</f>
         <v xml:space="preserve">---
 layout: reveal
-title: 'Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden? (Teil II)'
+title: 'Übungen: Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden?'
 author: 'Nathan Gibson'
 session: 12
 tags: [12,slides]
@@ -2274,14 +2386,16 @@
 # Einführung in die 
 ### Religionswissenschaft
 {: .r-fit-text}
-### Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden? (Teil II)
-Wintersemester 2025/2026
-Prof. Dr. Nathan Gibson
-## 📈 Rückblick: Lernziel
-## 📈 Rückblick: 
-## Projekt
-## Einleitung
-## Heutiges Lernziel
+### Übungen: Wie können LLMs für das Programmieren von Datenvisualisierung eingesetzt werden?
+Wintersemester 2025/2026
+Prof. Dr. Nathan Gibson
+## 📈 Rückblick: Lernziel
+Best Practices des Programmierens mit LLMs bezüglich Datenvisualisierung erfassen.
+## 📈 Rückblick: 
+## Projekt
+## Einleitung
+## Heutiges Lernziel
+Erfahrungen mit Datenvisualisierung sammeln.
 ## Lektüre
 ## Diskussion
 ## Vorschau

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25ki/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2161E74-A5C0-2744-8271-8DE313F64D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B96DE2-5803-DE47-861D-004FD0872AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -212,21 +212,9 @@
     <t>Maschinelles Lernen</t>
   </si>
   <si>
-    <t>Begriffe Datenreinigung und -analyse I</t>
-  </si>
-  <si>
     <t>Begriffe: Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden?</t>
   </si>
   <si>
-    <t>Übungen Datenreinigung und -analyse II</t>
-  </si>
-  <si>
-    <t>Begriffe Datenvisualisierung I</t>
-  </si>
-  <si>
-    <t>Übungen Datenvisualisierung II</t>
-  </si>
-  <si>
     <t>Übungen: Wie können LLMs für das Programmieren von Datenreinigung bzw. Datenanalyse eingesetzt werden?</t>
   </si>
   <si>
@@ -270,6 +258,18 @@
   </si>
   <si>
     <t>Die Grundcharakteristika von Large Language Models skizzieren.</t>
+  </si>
+  <si>
+    <t>Begriffe Datenreinigung und -analyse</t>
+  </si>
+  <si>
+    <t>Übungen Datenreinigung und -analyse</t>
+  </si>
+  <si>
+    <t>Begriffe Datenvisualisierung</t>
+  </si>
+  <si>
+    <t>Übungen Datenvisualisierung</t>
   </si>
 </sst>
 </file>
@@ -850,7 +850,7 @@
         <v>1-Vorstellung</v>
       </c>
       <c r="O2" s="17" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="Q2" t="str">
         <f t="shared" ref="Q2:Q13" si="4">"["&amp;B2&amp;"]"</f>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="N3" s="10"/>
       <c r="O3" s="17" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="Q3" t="str">
         <f t="shared" si="4"/>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="N4" s="10"/>
       <c r="O4" s="17" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="Q4" t="str">
         <f t="shared" si="4"/>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="N5" s="11"/>
       <c r="O5" s="17" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="Q5" t="str">
         <f t="shared" si="4"/>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="N6" s="15"/>
       <c r="O6" s="17" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="Q6" t="str">
         <f t="shared" si="4"/>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="N7" s="9"/>
       <c r="O7" s="17" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="Q7" t="str">
         <f t="shared" si="4"/>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="N8" s="12"/>
       <c r="O8" s="17" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="Q8" t="str">
         <f t="shared" si="4"/>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="N9" s="9"/>
       <c r="O9" s="17" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="Q9" t="str">
         <f t="shared" si="4"/>
@@ -1904,10 +1904,10 @@
         <v>37</v>
       </c>
       <c r="G10" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H10" t="s">
         <v>59</v>
-      </c>
-      <c r="H10" t="s">
-        <v>60</v>
       </c>
       <c r="J10" t="str">
         <f t="shared" si="1"/>
@@ -1922,11 +1922,11 @@
       </c>
       <c r="M10" t="str">
         <f t="shared" si="3"/>
-        <v>9-Begriffe-Datenreinigung-und-analyse-I</v>
+        <v>9-Begriffe-Datenreinigung-und-analyse</v>
       </c>
       <c r="N10" s="9"/>
       <c r="O10" s="17" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="Q10" t="str">
         <f t="shared" si="4"/>
@@ -2032,10 +2032,10 @@
         <v>37</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="H11" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="J11" t="str">
         <f t="shared" si="1"/>
@@ -2050,11 +2050,11 @@
       </c>
       <c r="M11" t="str">
         <f t="shared" si="3"/>
-        <v>10-Übungen-Datenreinigung-und-analyse-II</v>
+        <v>10-Übungen-Datenreinigung-und-analyse</v>
       </c>
       <c r="N11" s="9"/>
       <c r="O11" s="17" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q11" t="str">
         <f t="shared" si="4"/>
@@ -2160,10 +2160,10 @@
         <v>37</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="H12" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="J12" t="str">
         <f t="shared" si="1"/>
@@ -2178,11 +2178,11 @@
       </c>
       <c r="M12" t="str">
         <f t="shared" si="3"/>
-        <v>11-Begriffe-Datenvisualisierung-I</v>
+        <v>11-Begriffe-Datenvisualisierung</v>
       </c>
       <c r="N12" s="9"/>
       <c r="O12" s="17" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="Q12" t="str">
         <f t="shared" si="4"/>
@@ -2288,10 +2288,10 @@
         <v>37</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
@@ -2306,11 +2306,11 @@
       </c>
       <c r="M13" t="str">
         <f t="shared" si="3"/>
-        <v>12-Übungen-Datenvisualisierung-II</v>
+        <v>12-Übungen-Datenvisualisierung</v>
       </c>
       <c r="N13" s="9"/>
       <c r="O13" s="17" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="Q13" t="str">
         <f t="shared" si="4"/>
